--- a/output/lmm_all.xlsx
+++ b/output/lmm_all.xlsx
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22.94</v>
+        <v>18.291</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -588,7 +588,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.17</v>
+        <v>0.128</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>2.022</v>
+        <v>3.147</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -606,16 +606,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.006</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005</v>
+        <v>0.46</v>
       </c>
       <c r="M4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.008</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.308</v>
+        <v>3.168</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -640,7 +640,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -649,7 +649,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.434</v>
+        <v>2.89</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001</v>
+        <v>-0.032</v>
       </c>
       <c r="L5" t="n">
-        <v>0.609</v>
+        <v>0.007</v>
       </c>
       <c r="M5" t="n">
-        <v>0.761</v>
+        <v>0.01166666666666667</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.511</v>
+        <v>8.491</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -692,16 +692,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.076</v>
+        <v>0.043</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H6" t="n">
-        <v>1.844</v>
+        <v>3.234</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -710,16 +710,16 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.006</v>
+        <v>-0.039</v>
       </c>
       <c r="L6" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="M6" t="n">
-        <v>0.008</v>
+        <v>0.0075</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.655</v>
+        <v>1.503</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.041</v>
+        <v>0.035</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -753,7 +753,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.794</v>
+        <v>1.967</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -762,16 +762,16 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0</v>
+        <v>0.036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9389999999999999</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.001</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.665</v>
+        <v>3.664</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -796,16 +796,16 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.767</v>
       </c>
       <c r="H8" t="n">
-        <v>2.342</v>
+        <v>2.559</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -814,16 +814,16 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.008</v>
+        <v>-0.005</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.622</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.622</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/output/lmm_all.xlsx
+++ b/output/lmm_all.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,20 +479,6 @@
       </c>
       <c r="I1" s="1" t="n"/>
       <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Group x MONTH Cov</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>MONTH Var</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -541,36 +527,6 @@
           <t>pval_fdr</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>param</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>pval</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>pval_fdr</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>param</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>pval</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>pval_fdr</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -579,7 +535,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.291</v>
+        <v>13.703</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -588,39 +544,21 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.128</v>
+        <v>0.197</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
-        <v>3.147</v>
+        <v>14.124</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -631,7 +569,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.168</v>
+        <v>2.373</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -640,7 +578,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.032</v>
+        <v>0.033</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -649,30 +587,12 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.89</v>
+        <v>3.416</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.032</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.01166666666666667</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -683,7 +603,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8.491</v>
+        <v>6.265</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -692,39 +612,21 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.043</v>
+        <v>0.078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>3.234</v>
+        <v>3.602</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.039</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -735,7 +637,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.503</v>
+        <v>1.068</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -744,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -753,30 +655,12 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.967</v>
+        <v>2.085</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -787,7 +671,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.664</v>
+        <v>3.017</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -796,49 +680,29 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003</v>
+        <v>0.032</v>
       </c>
       <c r="F8" t="n">
-        <v>0.767</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.767</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.559</v>
+        <v>4.145</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.622</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="N1:P1"/>
     <mergeCell ref="E1:G1"/>
-    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/lmm_all.xlsx
+++ b/output/lmm_all.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,13 +472,6 @@
       </c>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Group Var</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -512,21 +505,6 @@
           <t>pval_fdr</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>param</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>pval</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>pval_fdr</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -535,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.703</v>
+        <v>14.337</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -544,22 +522,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.197</v>
+        <v>0.156</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>0.422</v>
       </c>
       <c r="G4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14.124</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="5">
@@ -569,7 +538,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.373</v>
+        <v>2.483</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -578,21 +547,12 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.033</v>
+        <v>0.029</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.416</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -603,7 +563,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.265</v>
+        <v>6.547</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -612,22 +572,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.078</v>
+        <v>0.065</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.602</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="7">
@@ -637,7 +588,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.068</v>
+        <v>1.156</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -646,21 +597,12 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.024</v>
+        <v>0.022</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.085</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -671,7 +613,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.017</v>
+        <v>3.102</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -680,27 +622,17 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.145</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H1:J1"/>
+  <mergeCells count="2">
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
   </mergeCells>

--- a/output/lmm_all.xlsx
+++ b/output/lmm_all.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,27 @@
       </c>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Group Var</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Group x MONTH Cov</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>MONTH Var</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -505,6 +526,51 @@
           <t>pval_fdr</t>
         </is>
       </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>pval_fdr</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>pval_fdr</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>param</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>pval</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>pval_fdr</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -513,7 +579,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14.337</v>
+        <v>21.144</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -522,13 +588,40 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.156</v>
+        <v>0.205</v>
       </c>
       <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.071</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="M4" t="n">
         <v>0.422</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.478</v>
+      <c r="N4" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.483</v>
+        <v>3.709</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -547,12 +640,39 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.029</v>
+        <v>0.043</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.013</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -563,7 +683,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.547</v>
+        <v>9.677</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -572,13 +692,40 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.065</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.478</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.478</v>
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.917</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -588,7 +735,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.156</v>
+        <v>1.627</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -597,12 +744,39 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.022</v>
+        <v>0.03</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.857</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2633333333333334</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -613,7 +787,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.102</v>
+        <v>4.524</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -622,19 +796,49 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.027</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.966</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
+    <mergeCell ref="H1:J1"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="N1:P1"/>
     <mergeCell ref="E1:G1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
